--- a/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bertrand rentre de l'école avec papa. Le soir, la cuisine sent le pain. Bertrand a les joues chaudes. Il pense à des rires dans la cour. Un camarade a ri d'un autre. Bertrand a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Maman dit : tu peux raconter. Raconter, c'est dire ce qui s'est passé. Bertrand dit : on a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute. Papa dit : même si on a ri, on raconte. Même si on a ri, maman est là. Bertrand raconte encore un peu. Il parle des rires, sans les imiter. Maman dit : merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bertrand boit de l'eau. Il se sent plus léger.</t>
+          <t>Bertrand rentre de l'école avec papa. Le soir, la cuisine sent le pain. Bertrand a les joues chaudes. Il pense à des rires dans la cour. Un camarade a ri d'un autre. Bertrand a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute. Même si on a ri, on raconte. Même si on a ri, maman est là. Bertrand raconte encore un peu. Il parle des rires, sans les imiter. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bertrand boit de l'eau. Il se sent plus léger.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Bertrand rentre de l'école avec papa. Le soir, la cuisine sent le pain. Bertrand a les joues chaudes. Il pense à des rires dans la cour. Un camarade a ri d'un autre. Bertrand a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi.
+maman|Tu peux raconter. Raconter, c'est dire ce qui s'est passé.
+enfant-m|On a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute.
+papa|Même si on a ri, on raconte. Même si on a ri, maman est là.
+narrateur|Bertrand raconte encore un peu. Il parle des rires, sans les imiter.
+maman|Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman.
+narrateur|Bertrand boit de l'eau. Il se sent plus léger.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Bertrand a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Bertrand a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Bertrand range son cartable. Maman lui tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Bertrand boit de l'eau. Il se sent plus léger.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Bertrand a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Bertrand a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Bertrand range son cartable. Maman lui tient la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bertrand raconte à maman</t>
+          <t>La bouilloire de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La bouilloire chante. Victorino rentre de l'école. Même s'il a ri un peu dans la cour, il raconte à maman et papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bertrand rentre de l'école avec papa. Le soir, la cuisine sent le pain. Bertrand a les joues chaudes. Il pense à des rires dans la cour. Un camarade a ri d'un autre. Bertrand a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute. Même si on a ri, on raconte. Même si on a ri, maman est là. Bertrand raconte encore un peu. Il parle des rires, sans les imiter. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bertrand boit de l'eau. Il se sent plus léger.</t>
+          <t>La bouilloire chante, toute ronde. La vapeur fait un petit nuage blanc. Des miettes de pain dorment sur la table. La gouttière chante aussi, dehors. L'eau glisse le long du toit. La chaise en bois attend, un peu de travers. Le couvercle de la bouilloire tremble un peu. Une miette colle sous le doigt de maman. L'eau est chaude, Victorino. Tes chaussures claquent dans l'entrée. Viens près de nous. En ce moment, Victorino rentre de l'école avec papa. Le soir, la cuisine sent le pain. Victorino a les joues chaudes. Il pense à des rires dans la cour. Dans la cour, il y a eu des rires. Victorino a ri un peu aussi. Son ventre est serré. Maman. Papa. Mon ventre est serré. Je m'assois près de toi. Moi aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute. Papa écoute. Même si on a ri, on raconte. Même si on a ri, maman t'écoute. Papa t'écoute aussi. Victorino raconte encore un peu. Il parle des rires, sans les imiter. C'était dans la cour. Ça a duré un peu. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bravo, Victorino. C'est du bon travail. Tu veux un peu d'eau chaude, dans le verre ? Un peu, maman. L'eau fait un bruit clair. Victorino boit. Il se sent plus léger. La bouilloire a fini de chanter. La gouttière chante encore, plus loin. On reste encore un peu ensemble ? Oui, papa. Près de la table. Les miettes restent sur le bois. La vapeur s'en va, tout doucement. Tu as raconté. Même si tu as ri. Oui, maman. On t'écoute encore, si tu veux. La gouttière chante plus bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Bertrand rentre de l'école avec papa. Le soir, la cuisine sent le pain. Bertrand a les joues chaudes. Il pense à des rires dans la cour. Un camarade a ri d'un autre. Bertrand a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi.
-maman|Tu peux raconter. Raconter, c'est dire ce qui s'est passé.
-enfant-m|On a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute.
-papa|Même si on a ri, on raconte. Même si on a ri, maman est là.
-narrateur|Bertrand raconte encore un peu. Il parle des rires, sans les imiter.
-maman|Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman.
-narrateur|Bertrand boit de l'eau. Il se sent plus léger.</t>
+          <t>narrateur|La bouilloire chante, toute ronde.
+narrateur|La vapeur fait un petit nuage blanc.
+narrateur|Des miettes de pain dorment sur la table.
+narrateur|La gouttière chante aussi, dehors.
+narrateur|L'eau glisse le long du toit.
+narrateur|La chaise en bois attend, un peu de travers.
+narrateur|Le couvercle de la bouilloire tremble un peu.
+narrateur|Une miette colle sous le doigt de maman.
+maman|L'eau est chaude, Victorino.
+papa|Tes chaussures claquent dans l'entrée.
+papa|Viens près de nous.
+narrateur|En ce moment, Victorino rentre de l'école avec papa.
+narrateur|Le soir, la cuisine sent le pain.
+narrateur|Victorino a les joues chaudes.
+narrateur|Il pense à des rires dans la cour.
+narrateur|Dans la cour, il y a eu des rires.
+narrateur|Victorino a ri un peu aussi.
+narrateur|Son ventre est serré.
+enfant-m|Maman.
+enfant-m|Papa.
+enfant-m|Mon ventre est serré.
+maman|Je m'assois près de toi.
+papa|Moi aussi.
+maman|Tu peux raconter.
+maman|Raconter, c'est dire ce qui s'est passé.
+enfant-m|On a ri.
+enfant-m|J'ai ri aussi.
+narrateur|Il ne répète pas les mots.
+narrateur|Maman écoute.
+narrateur|Papa écoute.
+papa|Même si on a ri, on raconte.
+papa|Même si on a ri, maman t'écoute.
+maman|Papa t'écoute aussi.
+narrateur|Victorino raconte encore un peu.
+narrateur|Il parle des rires, sans les imiter.
+enfant-m|C'était dans la cour.
+enfant-m|Ça a duré un peu.
+maman|Merci d'avoir raconté.
+maman|Même si on a ri, on raconte à papa ou maman.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+maman|Tu veux un peu d'eau chaude, dans le verre ?
+enfant-m|Un peu, maman.
+narrateur|L'eau fait un bruit clair.
+narrateur|Victorino boit.
+narrateur|Il se sent plus léger.
+papa|La bouilloire a fini de chanter.
+maman|La gouttière chante encore, plus loin.
+papa|On reste encore un peu ensemble ?
+enfant-m|Oui, papa.
+enfant-m|Près de la table.
+narrateur|Les miettes restent sur le bois.
+narrateur|La vapeur s'en va, tout doucement.
+maman|Tu as raconté.
+maman|Même si tu as ri.
+enfant-m|Oui, maman.
+papa|On t'écoute encore, si tu veux.
+narrateur|La gouttière chante plus bas.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bertrand a ri un peu. Que fait-il le soir ?</t>
+          <t>Victorino a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Bertrand a ri un peu. Que fait-il le soir ?</t>
+          <t>narrateur|Victorino a ri un peu.
+narrateur|Que fait-il le soir ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bertrand a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
+          <t>Victorino a su raconter. Même si on a ri, il a parlé à papa et maman. Tu es venu nous le dire. Bravo. C'est du bon travail, Victorino. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le ventre de Victorino se desserre. La bouilloire est calme, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1738,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Bertrand a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
+          <t>narrateur|Victorino a su raconter.
+narrateur|Même si on a ri, il a parlé à papa et maman.
+maman|Tu es venu nous le dire.
+maman|Bravo.
+papa|C'est du bon travail, Victorino.
+enfant-m|J'ai raconté.
+enfant-m|Même si j'ai ri.
+papa|Oui.
+papa|On raconte à papa ou maman.
+narrateur|Le ventre de Victorino se desserre.
+narrateur|La bouilloire est calme, maintenant.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bertrand range son cartable. Maman lui tient la main.</t>
+          <t>Victorino range son cartable. La sangle est encore un peu humide. Donne-moi ta main. Maman lui tient la main. Tes chaussures sèchent près de la porte. On reste encore un peu ? Oui, maman. Près de toi. La gouttière chante plus doucement. La cuisine est calme. Les miettes attendent d'être ramassées.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1916,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Bertrand range son cartable. Maman lui tient la main.</t>
+          <t>narrateur|Victorino range son cartable.
+narrateur|La sangle est encore un peu humide.
+maman|Donne-moi ta main.
+narrateur|Maman lui tient la main.
+papa|Tes chaussures sèchent près de la porte.
+maman|On reste encore un peu ?
+enfant-m|Oui, maman.
+enfant-m|Près de toi.
+papa|La gouttière chante plus doucement.
+narrateur|La cuisine est calme.
+narrateur|Les miettes attendent d'être ramassées.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. On t'a écouté. La bouilloire s'est tue. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2094,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté.
+enfant-m|Même si j'ai ri.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|On t'a écouté.
+narrateur|La bouilloire s'est tue.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La bouilloire chante, toute ronde. La vapeur fait un petit nuage blanc. Des miettes de pain dorment sur la table. La gouttière chante aussi, dehors. L'eau glisse le long du toit. La chaise en bois attend, un peu de travers. Le couvercle de la bouilloire tremble un peu. Une miette colle sous le doigt de maman. L'eau est chaude, Victorino. Tes chaussures claquent dans l'entrée. Viens près de nous. En ce moment, Victorino rentre de l'école avec papa. Le soir, la cuisine sent le pain. Victorino a les joues chaudes. Il pense à des rires dans la cour. Dans la cour, il y a eu des rires. Victorino a ri un peu aussi. Son ventre est serré. Maman. Papa. Mon ventre est serré. Je m'assois près de toi. Moi aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute. Papa écoute. Même si on a ri, on raconte. Même si on a ri, maman t'écoute. Papa t'écoute aussi. Victorino raconte encore un peu. Il parle des rires, sans les imiter. C'était dans la cour. Ça a duré un peu. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bravo, Victorino. C'est du bon travail. Tu veux un peu d'eau chaude, dans le verre ? Un peu, maman. L'eau fait un bruit clair. Victorino boit. Il se sent plus léger. La bouilloire a fini de chanter. La gouttière chante encore, plus loin. On reste encore un peu ensemble ? Oui, papa. Près de la table. Les miettes restent sur le bois. La vapeur s'en va, tout doucement. Tu as raconté. Même si tu as ri. Oui, maman. On t'écoute encore, si tu veux. La gouttière chante plus bas.</t>
+          <t>La bouilloire chante, toute ronde. La vapeur fait un petit nuage blanc. Des miettes de pain dorment sur la table. La gouttière chante aussi, dehors. L'eau glisse le long du toit. La chaise en bois attend, un peu de travers. Le couvercle de la bouilloire tremble un peu. Une miette colle sous le doigt de maman. L'eau est chaude, Victorino. Tes chaussures claquent dans l'entrée. Viens près de nous. En ce moment, Victorino rentre de l'école avec papa. Le soir, la cuisine sent le pain. Victorino a les joues chaudes. Il pense à des rires dans la cour. Dans la cour, il y a eu des rires. Victorino a ri un peu aussi. Son ventre est serré. Maman. Papa. Mon ventre est serré. Je m'assois près de toi. Moi aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute. Papa écoute. Même si on a ri, on raconte. Même si on a ri, maman t'écoute. Papa t'écoute aussi. Victorino raconte encore un peu. Il parle des rires, sans les imiter. C'était dans la cour. Ça a duré un peu. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bravo, Victorino. Tu veux un peu d'eau chaude, dans le verre ? Un peu, maman. L'eau fait un bruit clair. Victorino boit. Il se sent plus léger. La bouilloire a fini de chanter. La gouttière chante encore, plus loin. On reste encore un peu ensemble ? Oui, papa. Près de la table. Les miettes restent sur le bois. La vapeur s'en va, tout doucement. Tu as raconté. Même si tu as ri. Oui, maman. On t'écoute encore, si tu veux. La gouttière chante plus bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bertrand rentre de l'école avec papa. Le soir, la cuisine sent le pain. Bertrand a les joues chaudes. Il pense à des rires dans la cour. Un camarade a ri d'un autre. Bertrand a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Maman dit : tu peux &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Raconter, c'est dire ce qui s'est passé. Bertrand dit : on a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute. Papa dit : même si on a ri, on raconte. Même si on a ri, maman est là. Bertrand raconte encore un peu. Il parle des rires, sans les imiter. Maman dit : merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bertrand boit de l'eau. Il se sent plus léger.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La bouilloire chante, toute ronde. La vapeur fait un petit nuage blanc. Des miettes de pain dorment sur la table. La gouttière chante aussi, dehors. L'eau glisse le long du toit. La chaise en bois attend, un peu de travers. Le couvercle de la bouilloire tremble un peu. Une miette colle sous le doigt de maman. L'eau est chaude, Victorino. Tes chaussures claquent dans l'entrée. Viens près de nous. En ce moment, Victorino rentre de l'école avec papa. Le soir, la cuisine sent le pain. Victorino a les joues chaudes. Il pense à des rires dans la cour. Dans la cour, il y a eu des rires. Victorino a ri un peu aussi. Son ventre est serré. Maman. Papa. Mon ventre est serré. Je m'assois près de toi. Moi aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Il ne répète pas les mots. Maman écoute. Papa écoute. Même si on a ri, on raconte. Même si on a ri, maman t'écoute. Papa t'écoute aussi. Victorino raconte encore un peu. Il parle des rires, sans les imiter. C'était dans la cour. Ça a duré un peu. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bravo, Victorino. Tu veux un peu d'eau chaude, dans le verre ? Un peu, maman. L'eau fait un bruit clair. Victorino boit. Il se sent plus léger. La bouilloire a fini de chanter. La gouttière chante encore, plus loin. On reste encore un peu ensemble ? Oui, papa. Près de la table. Les miettes restent sur le bois. La vapeur s'en va, tout doucement. Tu as raconté. Même si tu as ri. Oui, maman. On t'écoute encore, si tu veux. La gouttière chante plus bas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 maman|Merci d'avoir raconté.
 maman|Même si on a ri, on raconte à papa ou maman.
 papa|Bravo, Victorino.
-papa|C'est du bon travail.
 maman|Tu veux un peu d'eau chaude, dans le verre ?
 enfant-m|Un peu, maman.
 narrateur|L'eau fait un bruit clair.
@@ -1384,7 +1383,6 @@
 narrateur|La gouttière chante plus bas.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1414,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bertrand a ri un peu. Que fait-il le soir ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1567,6 @@
 narrateur|Que fait-il le soir ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a su raconter. Même si on a ri, il a parlé à papa et maman. Tu es venu nous le dire. Bravo. C'est du bon travail, Victorino. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le ventre de Victorino se desserre. La bouilloire est calme, maintenant.</t>
+          <t>Victorino a su raconter. Même si on a ri, il a parlé à papa et maman. Tu es venu nous le dire. Bravo. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le ventre de Victorino se desserre. La bouilloire est calme, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bertrand a su &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Même si on a ri, il a parlé à papa et maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a su raconter. Même si on a ri, il a parlé à papa et maman. Tu es venu nous le dire. Bravo. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le ventre de Victorino se desserre. La bouilloire est calme, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,7 +1739,6 @@
 narrateur|Même si on a ri, il a parlé à papa et maman.
 maman|Tu es venu nous le dire.
 maman|Bravo.
-papa|C'est du bon travail, Victorino.
 enfant-m|J'ai raconté.
 enfant-m|Même si j'ai ri.
 papa|Oui.
@@ -1751,7 +1747,6 @@
 narrateur|La bouilloire est calme, maintenant.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,7 +1776,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bertrand range son cartable. Maman lui tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino range son cartable. La sangle est encore un peu humide. Donne-moi ta main. Maman lui tient la main. Tes chaussures sèchent près de la porte. On reste encore un peu ? Oui, maman. Près de toi. La gouttière chante plus doucement. La cuisine est calme. Les miettes attendent d'être ramassées.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1929,7 +1924,6 @@
 narrateur|Les miettes attendent d'être ramassées.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1954,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. On t'a écouté. La bouilloire s'est tue. L'histoire est finie.</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. On t'a écouté. La bouilloire s'est tue.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. On t'a écouté. La bouilloire s'est tue.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,13 +2091,10 @@
           <t>enfant-m|J'ai raconté.
 enfant-m|Même si j'ai ri.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 papa|On t'a écouté.
-narrateur|La bouilloire s'est tue.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La bouilloire s'est tue.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2122,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2158,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bertrand, papa, maman</t>
+          <t>Victorino, papa, maman</t>
         </is>
       </c>
     </row>
